--- a/变电站/2026年7月/收据/202房_7月收据.xlsx
+++ b/变电站/2026年7月/收据/202房_7月收据.xlsx
@@ -711,10 +711,10 @@
         <v>3398</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>3398</v>
+        <v>3400</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
@@ -724,7 +724,7 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n"/>
     </row>
@@ -805,7 +805,7 @@
     <row r="10" ht="28" customHeight="1" s="5">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>合计   人民币（大写）陆佰贰拾陆元整</t>
+          <t>合计   人民币（大写）陆佰贰拾捌元整</t>
         </is>
       </c>
       <c r="B10" s="14" t="n"/>
@@ -817,7 +817,7 @@
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>(¥：626元)</t>
+          <t>(¥：628元)</t>
         </is>
       </c>
       <c r="J10" s="14" t="n"/>
